--- a/output/pdf_financials_xlsx/BNXT.xlsx
+++ b/output/pdf_financials_xlsx/BNXT.xlsx
@@ -1912,13 +1912,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>4.020513</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>4.495332</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>6.031176</v>
       </c>
     </row>
     <row r="93">
@@ -3157,7 +3157,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="n">
         <v>4.020513</v>
       </c>

--- a/output/pdf_financials_xlsx/BNXT.xlsx
+++ b/output/pdf_financials_xlsx/BNXT.xlsx
@@ -616,7 +616,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000301</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -868,7 +868,7 @@
         <v>-7.722927</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.311505</v>
+        <v>-5.311806</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-7.025486</v>
@@ -900,7 +900,7 @@
         <v>-7.527164</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.219746</v>
+        <v>-5.220047</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-7.014583</v>
@@ -916,7 +916,7 @@
         <v>-2022.088559477981</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-19343.13878080415</v>
+        <v>-19344.2542153048</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -972,13 +972,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.363655</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.032352</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.055264</v>
       </c>
     </row>
     <row r="35">
@@ -1004,13 +1004,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.363655</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.032352</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.055264</v>
       </c>
     </row>
     <row r="37">
@@ -1196,13 +1196,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.436464</v>
+        <v>0.072809</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.103093</v>
+        <v>0.070741</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.243196</v>
+        <v>0.187932</v>
       </c>
     </row>
     <row r="49">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">

--- a/output/pdf_financials_xlsx/BNXT.xlsx
+++ b/output/pdf_financials_xlsx/BNXT.xlsx
@@ -2223,13 +2223,13 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.302261</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.056211</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.137432</v>
       </c>
     </row>
     <row r="113">
@@ -3672,7 +3672,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>0.046257</v>
       </c>
@@ -3912,7 +3916,11 @@
           <t>Proceeds from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E43" s="5" t="n">
         <v>0.302261</v>
       </c>

--- a/output/pdf_financials_xlsx/BNXT.xlsx
+++ b/output/pdf_financials_xlsx/BNXT.xlsx
@@ -677,13 +677,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-7.722927</v>
+        <v>-15.445854</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-5.311505</v>
+        <v>-10.7128</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-7.025486</v>
+        <v>-14.248441</v>
       </c>
     </row>
     <row r="17">
@@ -693,13 +693,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>7.722927</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>5.401295</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>7.222955</v>
       </c>
     </row>
     <row r="18">
@@ -865,13 +865,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-7.722927</v>
+        <v>-15.445854</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-5.311806</v>
+        <v>-10.713101</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-7.025486</v>
+        <v>-14.248441</v>
       </c>
     </row>
     <row r="28">
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-7.527164</v>
+        <v>-15.250091</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-5.220047</v>
+        <v>-10.621342</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-7.014583</v>
+        <v>-14.237538</v>
       </c>
     </row>
     <row r="30">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-2022.088559477981</v>
+        <v>-4096.766662995269</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-19344.2542153048</v>
+        <v>-39360.17046507319</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -931,13 +931,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-50</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-50.41907811216488</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-50.69294949531672</v>
       </c>
     </row>
     <row r="32">
@@ -1506,13 +1506,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.903965</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>2.973612</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>3.189367</v>
       </c>
     </row>
     <row r="68">
@@ -3734,7 +3734,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -6109,7 +6113,11 @@
           <t>Loss Before Income Tax Recovery</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E114" s="5" t="n">
         <v>-7.722927</v>
       </c>
